--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484629_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484629_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5753</v>
+        <v>1.9273</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5753</v>
+        <v>0.8057</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.1216</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5753</v>
+        <v>2.8638</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3251</v>
+        <v>-1.0727</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2502</v>
+        <v>3.9365</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5753</v>
+        <v>3.2872</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3251</v>
+        <v>-0.6817</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2502</v>
+        <v>3.9689</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0.4234</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0.391</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0.0324</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.8803</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.2674</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.6129</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2515</v>
+        <v>1.5753</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1426</v>
+        <v>1.5753</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3941</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8638</v>
+        <v>1.5753</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0727</v>
+        <v>0.3251</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9365</v>
+        <v>1.2502</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2872</v>
+        <v>1.5753</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6817</v>
+        <v>0.3251</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9689</v>
+        <v>1.2502</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4234</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.391</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0324</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1991</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2044</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.681</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8854</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>C. WHITSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3765</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1235</v>
+        <v>-1.0275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>1.7629</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5875</v>
+        <v>0.0789</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1564</v>
+        <v>0.2071</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.7438</v>
+        <v>-0.1282</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0251</v>
+        <v>-0.2443</v>
       </c>
       <c r="K4" t="n">
-        <v>1.839</v>
+        <v>0.2043</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.814</v>
+        <v>-0.4486</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6125</v>
+        <v>0.3232</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3173</v>
+        <v>0.0029</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0.3204</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5057</v>
+        <v>0.3895</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1485</v>
+        <v>0.0939</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6543</v>
+        <v>0.2956</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8246</v>
+        <v>0.6335</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8246</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2964</v>
+        <v>0.6408</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3366</v>
+        <v>0.0417</v>
       </c>
       <c r="F5" t="n">
-        <v>1.633</v>
+        <v>0.5991</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5325</v>
+        <v>-0.5875</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.933</v>
+        <v>2.1564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4005</v>
+        <v>-2.7438</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.5107</v>
+        <v>0.0251</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.0781</v>
+        <v>1.839</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4327</v>
+        <v>-1.814</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0217</v>
+        <v>-0.6125</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8549</v>
+        <v>0.3173</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0253</v>
+        <v>0.77</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0121</v>
+        <v>0.0166</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0132</v>
+        <v>0.7534</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7198</v>
+        <v>-0.8246</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1911</v>
+        <v>-0.8246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. WHITSON</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2628</v>
+        <v>-0.8266</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7285</v>
+        <v>-2.5587</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4657</v>
+        <v>1.7321</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0789</v>
+        <v>-2.5325</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2071</v>
+        <v>-2.933</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1282</v>
+        <v>0.4005</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2443</v>
+        <v>-2.5107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2043</v>
+        <v>-2.0781</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4486</v>
+        <v>-0.4327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3232</v>
+        <v>-0.0217</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0029</v>
+        <v>-0.8549</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3204</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6087</v>
+        <v>0.9023</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6071</v>
+        <v>0.79</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0017</v>
+        <v>0.1123</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6335</v>
+        <v>1.7198</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9554</v>
+        <v>1.9109</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>-0.1911</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9856</v>
+        <v>-0.9112</v>
       </c>
       <c r="E7" t="n">
         <v>-0.6245000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.361</v>
+        <v>-0.2867</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1188</v>
@@ -1000,13 +1000,13 @@
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1337</v>
+        <v>-0.0594</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0043</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7012</v>
+        <v>-1.3493</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0649</v>
+        <v>-2.7625</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3636</v>
+        <v>1.4132</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6534</v>
@@ -1078,13 +1078,13 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1133</v>
+        <v>0.2387</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3122</v>
+        <v>-0.0098</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1989</v>
+        <v>0.2485</v>
       </c>
       <c r="V8" t="n">
         <v>0.432</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.833</v>
+        <v>-2.6047</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4823</v>
+        <v>-5.0558</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6493</v>
+        <v>2.4511</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3924</v>
@@ -1156,13 +1156,13 @@
         <v>2.5656</v>
       </c>
       <c r="S9" t="n">
-        <v>0.803</v>
+        <v>1.0313</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0151</v>
+        <v>0.4416</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7879</v>
+        <v>0.5897</v>
       </c>
       <c r="V9" t="n">
         <v>-2.0603</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4013</v>
+        <v>-4.4343</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3052</v>
+        <v>-5.1401</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9039</v>
+        <v>0.7058</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3825</v>
@@ -1234,13 +1234,13 @@
         <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2045</v>
+        <v>-0.2376</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.552</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.3144</v>
       </c>
       <c r="V10" t="n">
         <v>0.3011</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5641</v>
+        <v>-5.3494</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9699</v>
+        <v>-4.8047</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5942</v>
+        <v>-0.5447</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2695</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1999</v>
+        <v>0.365</v>
       </c>
       <c r="U11" t="n">
-        <v>0.346</v>
+        <v>0.3955</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4581</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.2483</v>
+        <v>-10.5967</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.2027</v>
+        <v>-19.5511</v>
       </c>
       <c r="F12" t="n">
         <v>8.9544</v>
@@ -1357,7 +1357,7 @@
         <v>-5.4186</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8545</v>
+        <v>-2.854499999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-2.5641</v>
@@ -1375,7 +1375,7 @@
         <v>-1.4381</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4744999999999999</v>
+        <v>-0.4745</v>
       </c>
       <c r="O12" t="n">
         <v>-0.9636999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>12.8282</v>
       </c>
       <c r="S12" t="n">
-        <v>3.024100000000001</v>
+        <v>4.675699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2939999999999999</v>
+        <v>1.3576</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3179</v>
+        <v>3.318</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5236</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0427</v>
+        <v>5.4657</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0216</v>
+        <v>1.4226</v>
       </c>
       <c r="F13" t="n">
-        <v>5.0643</v>
+        <v>4.0432</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9854</v>
+        <v>4.9922</v>
       </c>
       <c r="H13" t="n">
-        <v>1.36</v>
+        <v>2.9731</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6254</v>
+        <v>2.0192</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1066</v>
+        <v>4.0587</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9937</v>
+        <v>1.975</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1129</v>
+        <v>2.0837</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8787</v>
+        <v>0.9335</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3662</v>
+        <v>0.998</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5125</v>
+        <v>-0.0646</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3823</v>
+        <v>0.733</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2986</v>
+        <v>2.5656</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0519</v>
+        <v>-0.5815</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5339</v>
+        <v>-1.1255</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5858</v>
+        <v>0.5441</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="W13" t="n">
         <v>0.3219</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9103</v>
+        <v>5.3894</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6062</v>
+        <v>0.2669</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3041</v>
+        <v>5.1225</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6686</v>
+        <v>1.9854</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1589</v>
+        <v>1.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.6254</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6357</v>
+        <v>1.1066</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7927</v>
+        <v>0.9937</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.157</v>
+        <v>0.1129</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0329</v>
+        <v>0.8787</v>
       </c>
       <c r="N14" t="n">
         <v>0.3662</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6667</v>
+        <v>0.5125</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1991</v>
+        <v>3.2986</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1971</v>
+        <v>0.3986</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4261</v>
+        <v>-0.2454</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.229</v>
+        <v>0.644</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X14" t="n">
         <v>0.3011</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6849</v>
+        <v>4.0653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7495000000000001</v>
+        <v>-0.6438</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9354</v>
+        <v>4.7092</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9922</v>
+        <v>3.6686</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9731</v>
+        <v>3.1589</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0192</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0587</v>
+        <v>1.6357</v>
       </c>
       <c r="K15" t="n">
-        <v>1.975</v>
+        <v>2.7927</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0837</v>
+        <v>-1.157</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9335</v>
+        <v>2.0329</v>
       </c>
       <c r="N15" t="n">
-        <v>0.998</v>
+        <v>0.3662</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0646</v>
+        <v>1.6667</v>
       </c>
       <c r="P15" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5656</v>
+        <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3623</v>
+        <v>0.3522</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7986</v>
+        <v>0.1761</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4363</v>
+        <v>0.1761</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3219</v>
+        <v>-0.3219</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9695</v>
+        <v>2.5246</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6374</v>
+        <v>-0.5412</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6069</v>
+        <v>3.0658</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5569</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1413</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7722</v>
+        <v>-0.6761</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.369</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>2.2016</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4603</v>
+        <v>0.9026</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6413</v>
+        <v>-0.0357</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1016</v>
+        <v>0.9383</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3087</v>
+        <v>-0.103</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6627</v>
+        <v>-1.0584</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9714</v>
+        <v>0.9553</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7598</v>
+        <v>0.059</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2761</v>
+        <v>-1.217</v>
       </c>
       <c r="L17" t="n">
-        <v>2.036</v>
+        <v>1.276</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5489000000000001</v>
+        <v>-0.162</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.1587</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0646</v>
+        <v>-0.3207</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9321</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3878</v>
+        <v>-0.4996</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9193</v>
+        <v>-0.1338</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5315</v>
+        <v>-0.3658</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6439</v>
+        <v>0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>1.267</v>
+        <v>0.9554</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4513</v>
+        <v>0.834</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8334</v>
+        <v>-1.6511</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2847</v>
+        <v>2.4851</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2021</v>
+        <v>-1.0202</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9231</v>
+        <v>-1.7446</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.279</v>
+        <v>0.7244</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4387</v>
+        <v>-1.7314</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4804</v>
+        <v>-1.8147</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0417</v>
+        <v>0.0833</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7633</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4427</v>
+        <v>0.0701</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3207</v>
+        <v>0.641</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3497</v>
+        <v>-0.4678</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5008</v>
+        <v>-0.5924</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1511</v>
+        <v>0.1246</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0208</v>
+        <v>1.5889</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0208</v>
+        <v>1.5889</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3868</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3242</v>
+        <v>-1.3528</v>
       </c>
       <c r="F19" t="n">
-        <v>0.711</v>
+        <v>2.1598</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.103</v>
+        <v>1.3087</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0584</v>
+        <v>-0.6627</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9553</v>
+        <v>1.9714</v>
       </c>
       <c r="J19" t="n">
-        <v>0.059</v>
+        <v>0.7598</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.217</v>
+        <v>-1.2761</v>
       </c>
       <c r="L19" t="n">
-        <v>1.276</v>
+        <v>2.036</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.162</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1587</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3207</v>
+        <v>-0.0646</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>2.9321</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0154</v>
+        <v>-0.0411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4223</v>
+        <v>-0.6308</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5931</v>
+        <v>0.5897</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9554</v>
+        <v>-0.6439</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.343</v>
+        <v>0.3251</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9396</v>
+        <v>0.3251</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2826</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0202</v>
+        <v>0.3251</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7446</v>
+        <v>0.3251</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7244</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7314</v>
+        <v>0.3251</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8147</v>
+        <v>0.3251</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7112000000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0701</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.641</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9587</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8808</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0779</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3251</v>
+        <v>-0.6516</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3251</v>
+        <v>-1.8911</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.2395</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3251</v>
+        <v>-2.2021</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3251</v>
+        <v>-1.9231</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.279</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3251</v>
+        <v>-1.4387</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3251</v>
+        <v>-1.4804</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.7633</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.4427</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.3207</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.2468</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.4431</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.1963</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6573</v>
+        <v>-2.1458</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6976</v>
+        <v>-3.4091</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0403</v>
+        <v>1.2633</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1272</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3468</v>
+        <v>0.1646</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3673</v>
+        <v>-0.0788</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0204</v>
+        <v>0.2434</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6683</v>
+        <v>-3.3448</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5401</v>
+        <v>-1.444</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1281</v>
+        <v>-1.9008</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8521</v>
@@ -2248,13 +2248,13 @@
         <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4106</v>
+        <v>-0.0871</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5505</v>
+        <v>-0.4544</v>
       </c>
       <c r="U23" t="n">
-        <v>0.14</v>
+        <v>0.3673</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2224</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12.2483</v>
+        <v>14.1715</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.954400000000001</v>
+        <v>-8.9542</v>
       </c>
       <c r="F24" t="n">
-        <v>21.2028</v>
+        <v>23.1259</v>
       </c>
       <c r="G24" t="n">
         <v>5.418500000000002</v>
@@ -2299,16 +2299,16 @@
         <v>2.5641</v>
       </c>
       <c r="J24" t="n">
-        <v>1.438100000000001</v>
+        <v>1.4381</v>
       </c>
       <c r="K24" t="n">
         <v>0.4743000000000003</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9638000000000002</v>
+        <v>0.9637999999999998</v>
       </c>
       <c r="M24" t="n">
-        <v>3.980600000000001</v>
+        <v>3.9806</v>
       </c>
       <c r="N24" t="n">
         <v>2.38</v>
@@ -2326,19 +2326,19 @@
         <v>20.1582</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.0242</v>
+        <v>-1.1011</v>
       </c>
       <c r="T24" t="n">
         <v>-3.318000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2939000000000001</v>
+        <v>2.217</v>
       </c>
       <c r="V24" t="n">
         <v>2.5235</v>
       </c>
       <c r="W24" t="n">
-        <v>5.753299999999999</v>
+        <v>5.7533</v>
       </c>
       <c r="X24" t="n">
         <v>-3.23</v>
